--- a/mainWidget/mainWidget/src/database/壳体非金属材料.xlsx
+++ b/mainWidget/mainWidget/src/database/壳体非金属材料.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9303"/>
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13320"/>
@@ -10,16 +10,69 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="145621"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+  <si>
+    <t>等效弹性模量E1[MPa]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>等效弹性模量E2[MPa]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>等效弹性模量E3[MPa]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>等效泊松比Nu12</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>等效泊松比Nu13</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>等效泊松比Nu23</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>等效剪切模量G12[MPa]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>等效剪切模量G23[MPa]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>112422</t>
+  </si>
+  <si>
+    <t>15743</t>
+  </si>
+  <si>
+    <t>0.184</t>
+  </si>
+  <si>
+    <t>0.029</t>
+  </si>
+  <si>
+    <t>15783</t>
+  </si>
+  <si>
+    <t>5892</t>
+  </si>
+  <si>
+    <t>0.14</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>等效剪切模量G13[MPa]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
   <si>
     <r>
       <rPr>
@@ -32,7 +85,6 @@
       </rPr>
       <t>序号</t>
     </r>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -46,76 +98,229 @@
       </rPr>
       <t>材料牌号</t>
     </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>等效弹性模量E1[MPa]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>等效弹性模量E2[MPa]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>等效弹性模量E3[MPa]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>等效泊松比Nu12</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>等效泊松比Nu13</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>等效泊松比Nu23</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>等效剪切模量G12[MPa]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>等效剪切模量G23[MPa]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>112422</t>
-  </si>
-  <si>
-    <t>15743</t>
-  </si>
-  <si>
-    <t>0.184</t>
-  </si>
-  <si>
-    <t>0.029</t>
-  </si>
-  <si>
-    <t>15783</t>
-  </si>
-  <si>
-    <t>5892</t>
-  </si>
-  <si>
-    <t>0.14</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>等效剪切模量G13[MPa]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>碳纤维材料</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="仿宋"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>密度</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>[kg/m^3]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="仿宋"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>热膨胀系数</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>[/</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="仿宋"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>℃</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="仿宋"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>屈服强度</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>[MPa]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="仿宋"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>抗拉强度</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>[MPa]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="仿宋"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>热导率</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>[W/(m∙</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="仿宋"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>℃</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>)]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="仿宋"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>比热容</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>[J/(kg∙</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="仿宋"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>℃</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>)]</t>
+    </r>
+  </si>
+  <si>
+    <t>ASTM A36</t>
+  </si>
+  <si>
+    <t>0.000012</t>
+  </si>
+  <si>
+    <t>250</t>
+  </si>
+  <si>
+    <t>50.2</t>
+  </si>
+  <si>
+    <t>486</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -145,11 +350,15 @@
       <family val="1"/>
     </font>
     <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="仿宋"/>
-      <family val="3"/>
-      <charset val="134"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -197,36 +406,37 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="常规 2" xfId="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -487,7 +697,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -495,89 +705,125 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:Q2"/>
   <sheetFormatPr defaultRowHeight="14.15" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="15.78515625" customWidth="1"/>
-    <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="22.42578125" style="4" customWidth="1"/>
-    <col min="5" max="5" width="24.28515625" style="4" customWidth="1"/>
-    <col min="6" max="6" width="19.640625" style="4" customWidth="1"/>
-    <col min="7" max="7" width="18.78515625" style="4" customWidth="1"/>
-    <col min="8" max="8" width="16" style="4" customWidth="1"/>
-    <col min="9" max="9" width="23.0703125" style="4" customWidth="1"/>
-    <col min="10" max="10" width="21.640625" style="4" customWidth="1"/>
-    <col min="11" max="11" width="28.7109375" customWidth="1"/>
+    <col min="2" max="2" width="17.85546875" customWidth="1"/>
+    <col min="3" max="3" width="22.42578125" customWidth="1"/>
+    <col min="4" max="6" width="19.78515625" customWidth="1"/>
+    <col min="7" max="9" width="17" customWidth="1"/>
+    <col min="10" max="12" width="19.5" customWidth="1"/>
+    <col min="13" max="13" width="21.5703125" customWidth="1"/>
+    <col min="14" max="14" width="18.5703125" customWidth="1"/>
+    <col min="15" max="15" width="17.0703125" customWidth="1"/>
+    <col min="16" max="16" width="13.35546875" customWidth="1"/>
+    <col min="17" max="17" width="21" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="15.9" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" t="s">
+    <row r="1" spans="1:17" ht="31.3" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="F1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="G1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="H1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="L1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="M1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
+      <c r="N1" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="O1" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="P1" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q1" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" ht="15.9" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="3">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" s="3">
+        <v>7850</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2" s="1">
+        <v>81478</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
-        <v>17</v>
-      </c>
-      <c r="K1" t="s">
+      <c r="G2" s="2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" ht="30.45" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="1">
-        <v>1</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C2" s="2">
-        <v>81478</v>
-      </c>
-      <c r="D2" s="3" t="s">
+      <c r="H2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="J2" s="4">
+        <v>7650</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="M2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="K2" s="3">
-        <v>7650</v>
+      <c r="N2" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="O2" s="4">
+        <v>475</v>
+      </c>
+      <c r="P2" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q2" s="4" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
